--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1189"/>
+  <dimension ref="A1:F1190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24192,19 +24192,39 @@
         <v>46276</v>
       </c>
       <c r="B1189" t="n">
-        <v>12.45</v>
+        <v>12.44999980926514</v>
       </c>
       <c r="C1189" t="n">
-        <v>12.85</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="D1189" t="n">
-        <v>12.29</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="E1189" t="n">
-        <v>12.83</v>
+        <v>12.82999992370605</v>
       </c>
       <c r="F1189" t="n">
         <v>10821188</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>6032797</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1190"/>
+  <dimension ref="A1:F1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24212,19 +24212,39 @@
         <v>46279</v>
       </c>
       <c r="B1190" t="n">
-        <v>12.26</v>
+        <v>12.26000022888184</v>
       </c>
       <c r="C1190" t="n">
-        <v>12.41</v>
+        <v>12.40999984741211</v>
       </c>
       <c r="D1190" t="n">
-        <v>12.23</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="E1190" t="n">
-        <v>12.41</v>
+        <v>12.40999984741211</v>
       </c>
       <c r="F1190" t="n">
         <v>6032797</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>5548618</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1191"/>
+  <dimension ref="A1:F1192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24232,19 +24232,39 @@
         <v>46280</v>
       </c>
       <c r="B1191" t="n">
-        <v>12.14</v>
+        <v>12.14000034332275</v>
       </c>
       <c r="C1191" t="n">
-        <v>12.31</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="D1191" t="n">
-        <v>12.03</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="E1191" t="n">
-        <v>12.3</v>
+        <v>12.30000019073486</v>
       </c>
       <c r="F1191" t="n">
         <v>5548618</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>13181988</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1192"/>
+  <dimension ref="A1:F1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24252,19 +24252,39 @@
         <v>46281</v>
       </c>
       <c r="B1192" t="n">
-        <v>11.74</v>
+        <v>11.73999977111816</v>
       </c>
       <c r="C1192" t="n">
-        <v>12.1</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="D1192" t="n">
-        <v>11.64</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="E1192" t="n">
-        <v>12.06</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F1192" t="n">
         <v>13181988</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>12958309</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1193"/>
+  <dimension ref="A1:F1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24271,20 +24271,32 @@
       <c r="A1193" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1193" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="C1193" t="n">
-        <v>12</v>
-      </c>
-      <c r="D1193" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="E1193" t="n">
-        <v>11.93</v>
-      </c>
+      <c r="B1193" t="inlineStr"/>
+      <c r="C1193" t="inlineStr"/>
+      <c r="D1193" t="inlineStr"/>
+      <c r="E1193" t="inlineStr"/>
       <c r="F1193" t="n">
-        <v>12958309</v>
+        <v>12480763</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1194" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>12516470</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1194"/>
+  <dimension ref="A1:F1195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24271,12 +24271,20 @@
       <c r="A1193" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1193" t="inlineStr"/>
-      <c r="C1193" t="inlineStr"/>
-      <c r="D1193" t="inlineStr"/>
-      <c r="E1193" t="inlineStr"/>
+      <c r="B1193" t="n">
+        <v>11.85000038146973</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>11.6899995803833</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>11.93000030517578</v>
+      </c>
       <c r="F1193" t="n">
-        <v>12480763</v>
+        <v>12958309</v>
       </c>
     </row>
     <row r="1194">
@@ -24284,19 +24292,39 @@
         <v>46283</v>
       </c>
       <c r="B1194" t="n">
-        <v>11.71</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="C1194" t="n">
-        <v>11.8</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="D1194" t="n">
-        <v>11.6</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1194" t="n">
-        <v>11.76</v>
+        <v>11.76000022888184</v>
       </c>
       <c r="F1194" t="n">
         <v>12516470</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1195" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>8883204</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1195"/>
+  <dimension ref="A1:F1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24312,19 +24312,39 @@
         <v>46286</v>
       </c>
       <c r="B1195" t="n">
-        <v>11.87</v>
+        <v>11.86999988555908</v>
       </c>
       <c r="C1195" t="n">
-        <v>11.91</v>
+        <v>11.90999984741211</v>
       </c>
       <c r="D1195" t="n">
-        <v>11.6</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="E1195" t="n">
-        <v>11.73</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="F1195" t="n">
         <v>8883204</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>8811298</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1196"/>
+  <dimension ref="A1:F1197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24332,19 +24332,39 @@
         <v>46287</v>
       </c>
       <c r="B1196" t="n">
-        <v>12.03</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="C1196" t="n">
-        <v>12.03</v>
+        <v>12.02999973297119</v>
       </c>
       <c r="D1196" t="n">
-        <v>11.65</v>
+        <v>11.64999961853027</v>
       </c>
       <c r="E1196" t="n">
-        <v>11.98</v>
+        <v>11.97999954223633</v>
       </c>
       <c r="F1196" t="n">
         <v>8811298</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>10445355</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1197"/>
+  <dimension ref="A1:F1198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24352,19 +24352,39 @@
         <v>46288</v>
       </c>
       <c r="B1197" t="n">
-        <v>11.64</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="C1197" t="n">
-        <v>12.15</v>
+        <v>12.14999961853027</v>
       </c>
       <c r="D1197" t="n">
-        <v>11.61</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="E1197" t="n">
-        <v>11.9</v>
+        <v>11.89999961853027</v>
       </c>
       <c r="F1197" t="n">
         <v>10445355</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1198" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>5080296</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1198"/>
+  <dimension ref="A1:F1199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24372,19 +24372,39 @@
         <v>46289</v>
       </c>
       <c r="B1198" t="n">
-        <v>11.62</v>
+        <v>11.61999988555908</v>
       </c>
       <c r="C1198" t="n">
-        <v>11.73</v>
+        <v>11.72999954223633</v>
       </c>
       <c r="D1198" t="n">
         <v>11.5</v>
       </c>
       <c r="E1198" t="n">
-        <v>11.64</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="F1198" t="n">
         <v>5080296</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>7124754</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1199"/>
+  <dimension ref="A1:F1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24392,19 +24392,39 @@
         <v>46290</v>
       </c>
       <c r="B1199" t="n">
-        <v>11.63</v>
+        <v>11.63000011444092</v>
       </c>
       <c r="C1199" t="n">
-        <v>11.81</v>
+        <v>11.8100004196167</v>
       </c>
       <c r="D1199" t="n">
-        <v>11.58</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="E1199" t="n">
-        <v>11.74</v>
+        <v>11.73999977111816</v>
       </c>
       <c r="F1199" t="n">
         <v>7124754</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>26867404</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1200"/>
+  <dimension ref="A1:F1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24412,19 +24412,39 @@
         <v>46293</v>
       </c>
       <c r="B1200" t="n">
-        <v>10.61</v>
+        <v>10.60999965667725</v>
       </c>
       <c r="C1200" t="n">
-        <v>11.1</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="D1200" t="n">
-        <v>10.61</v>
+        <v>10.60999965667725</v>
       </c>
       <c r="E1200" t="n">
-        <v>11.1</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="F1200" t="n">
         <v>26867404</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>13128576</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1201"/>
+  <dimension ref="A1:F1202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24432,19 +24432,39 @@
         <v>46294</v>
       </c>
       <c r="B1201" t="n">
-        <v>10.69</v>
+        <v>10.6899995803833</v>
       </c>
       <c r="C1201" t="n">
-        <v>10.82</v>
+        <v>10.81999969482422</v>
       </c>
       <c r="D1201" t="n">
-        <v>10.51</v>
+        <v>10.5600004196167</v>
       </c>
       <c r="E1201" t="n">
-        <v>10.72</v>
+        <v>10.72000026702881</v>
       </c>
       <c r="F1201" t="n">
         <v>13128576</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>16559908</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1202"/>
+  <dimension ref="A1:F1203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24452,19 +24452,39 @@
         <v>46295</v>
       </c>
       <c r="B1202" t="n">
-        <v>10.95</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="C1202" t="n">
-        <v>10.95</v>
+        <v>10.94999980926514</v>
       </c>
       <c r="D1202" t="n">
-        <v>10.45</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="E1202" t="n">
-        <v>10.74</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="F1202" t="n">
         <v>16559908</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>17780018</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1203"/>
+  <dimension ref="A1:F1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24472,19 +24472,39 @@
         <v>46296</v>
       </c>
       <c r="B1203" t="n">
-        <v>11.48</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="C1203" t="n">
         <v>11.5</v>
       </c>
       <c r="D1203" t="n">
-        <v>11.06</v>
+        <v>11.0600004196167</v>
       </c>
       <c r="E1203" t="n">
-        <v>11.45</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="F1203" t="n">
         <v>17780018</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>10818169</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1204"/>
+  <dimension ref="A1:F1205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24492,19 +24492,39 @@
         <v>46297</v>
       </c>
       <c r="B1204" t="n">
-        <v>11.71</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="C1204" t="n">
-        <v>11.71</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="D1204" t="n">
-        <v>11.24</v>
+        <v>11.23999977111816</v>
       </c>
       <c r="E1204" t="n">
-        <v>11.57</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="F1204" t="n">
         <v>10818169</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>28999945</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1205"/>
+  <dimension ref="A1:F1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24512,19 +24512,39 @@
         <v>46300</v>
       </c>
       <c r="B1205" t="n">
-        <v>12.6</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="C1205" t="n">
-        <v>12.8</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="D1205" t="n">
-        <v>12.31</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="E1205" t="n">
-        <v>12.55</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="F1205" t="n">
         <v>28999945</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>24301139</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1206"/>
+  <dimension ref="A1:F1207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24535,16 +24535,36 @@
         <v>13</v>
       </c>
       <c r="C1206" t="n">
-        <v>13.03</v>
+        <v>13.02999973297119</v>
       </c>
       <c r="D1206" t="n">
-        <v>12.6</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="E1206" t="n">
-        <v>12.6</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="F1206" t="n">
         <v>24301139</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>13815472</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1207"/>
+  <dimension ref="A1:F1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24552,19 +24552,39 @@
         <v>46302</v>
       </c>
       <c r="B1207" t="n">
-        <v>13.07</v>
+        <v>13.06999969482422</v>
       </c>
       <c r="C1207" t="n">
-        <v>13.1</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="D1207" t="n">
-        <v>12.81</v>
+        <v>12.8100004196167</v>
       </c>
       <c r="E1207" t="n">
-        <v>12.87</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="F1207" t="n">
         <v>13815472</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>12709521</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1208"/>
+  <dimension ref="A1:F1209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24572,19 +24572,39 @@
         <v>46303</v>
       </c>
       <c r="B1208" t="n">
-        <v>12.94</v>
+        <v>12.9399995803833</v>
       </c>
       <c r="C1208" t="n">
-        <v>13.18</v>
+        <v>13.18000030517578</v>
       </c>
       <c r="D1208" t="n">
-        <v>12.87</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="E1208" t="n">
-        <v>12.94</v>
+        <v>12.9399995803833</v>
       </c>
       <c r="F1208" t="n">
         <v>12709521</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>17869815</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -24592,13 +24592,13 @@
         <v>46304</v>
       </c>
       <c r="B1209" t="n">
-        <v>13.28</v>
+        <v>13.27999973297119</v>
       </c>
       <c r="C1209" t="n">
-        <v>13.37</v>
+        <v>13.36999988555908</v>
       </c>
       <c r="D1209" t="n">
-        <v>12.9</v>
+        <v>12.90999984741211</v>
       </c>
       <c r="E1209" t="n">
         <v>13</v>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1209"/>
+  <dimension ref="A1:F1210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24607,6 +24607,26 @@
         <v>17869815</v>
       </c>
     </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>12957970</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1210"/>
+  <dimension ref="A1:F1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24612,19 +24612,39 @@
         <v>46308</v>
       </c>
       <c r="B1210" t="n">
-        <v>13.08</v>
+        <v>13.07999992370605</v>
       </c>
       <c r="C1210" t="n">
-        <v>13.29</v>
+        <v>13.28999996185303</v>
       </c>
       <c r="D1210" t="n">
-        <v>13.05</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="E1210" t="n">
-        <v>13.28</v>
+        <v>13.27999973297119</v>
       </c>
       <c r="F1210" t="n">
         <v>12957970</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1211" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>16876372</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1211"/>
+  <dimension ref="A1:F1212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24632,19 +24632,39 @@
         <v>46309</v>
       </c>
       <c r="B1211" t="n">
-        <v>12.54</v>
+        <v>12.53999996185303</v>
       </c>
       <c r="C1211" t="n">
-        <v>12.96</v>
+        <v>12.96000003814697</v>
       </c>
       <c r="D1211" t="n">
-        <v>12.45</v>
+        <v>12.44999980926514</v>
       </c>
       <c r="E1211" t="n">
-        <v>12.9</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="F1211" t="n">
         <v>16876372</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>13710499</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1212"/>
+  <dimension ref="A1:F1213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24652,19 +24652,39 @@
         <v>46310</v>
       </c>
       <c r="B1212" t="n">
-        <v>12.55</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="C1212" t="n">
-        <v>12.67</v>
+        <v>12.67000007629395</v>
       </c>
       <c r="D1212" t="n">
-        <v>12.17</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="E1212" t="n">
-        <v>12.4</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="F1212" t="n">
         <v>13710499</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>16249784</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1213"/>
+  <dimension ref="A1:F1214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24672,19 +24672,39 @@
         <v>46311</v>
       </c>
       <c r="B1213" t="n">
-        <v>12.37</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="C1213" t="n">
-        <v>12.67</v>
+        <v>12.67000007629395</v>
       </c>
       <c r="D1213" t="n">
+        <v>12.26000022888184</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>12.57999992370605</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>16244434</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1214" t="n">
         <v>12.26</v>
       </c>
-      <c r="E1213" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="F1213" t="n">
-        <v>16249784</v>
+      <c r="C1214" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>15113420</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1214"/>
+  <dimension ref="A1:F1215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24692,19 +24692,39 @@
         <v>46314</v>
       </c>
       <c r="B1214" t="n">
-        <v>12.26</v>
+        <v>12.26000022888184</v>
       </c>
       <c r="C1214" t="n">
-        <v>12.59</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="D1214" t="n">
-        <v>12.14</v>
+        <v>12.14000034332275</v>
       </c>
       <c r="E1214" t="n">
-        <v>12.49</v>
+        <v>12.48999977111816</v>
       </c>
       <c r="F1214" t="n">
         <v>15113420</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>17804797</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1215"/>
+  <dimension ref="A1:F1216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24712,19 +24712,39 @@
         <v>46315</v>
       </c>
       <c r="B1215" t="n">
-        <v>12.73</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="C1215" t="n">
-        <v>12.88</v>
+        <v>12.88000011444092</v>
       </c>
       <c r="D1215" t="n">
         <v>12.25</v>
       </c>
       <c r="E1215" t="n">
-        <v>12.35</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="F1215" t="n">
         <v>17804797</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1216" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>12676120</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1216"/>
+  <dimension ref="A1:F1217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24732,19 +24732,39 @@
         <v>46316</v>
       </c>
       <c r="B1216" t="n">
-        <v>12.74</v>
+        <v>12.73999977111816</v>
       </c>
       <c r="C1216" t="n">
-        <v>12.93</v>
+        <v>12.93000030517578</v>
       </c>
       <c r="D1216" t="n">
-        <v>12.65</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="E1216" t="n">
-        <v>12.74</v>
+        <v>12.73999977111816</v>
       </c>
       <c r="F1216" t="n">
         <v>12676120</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>10672094</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1217"/>
+  <dimension ref="A1:F1218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24752,19 +24752,39 @@
         <v>46317</v>
       </c>
       <c r="B1217" t="n">
-        <v>12.48</v>
+        <v>12.47999954223633</v>
       </c>
       <c r="C1217" t="n">
-        <v>12.68</v>
+        <v>12.68000030517578</v>
       </c>
       <c r="D1217" t="n">
-        <v>12.34</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="E1217" t="n">
-        <v>12.56</v>
+        <v>12.5600004196167</v>
       </c>
       <c r="F1217" t="n">
         <v>10672094</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>17814604</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1218"/>
+  <dimension ref="A1:F1219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24772,19 +24772,39 @@
         <v>46318</v>
       </c>
       <c r="B1218" t="n">
-        <v>12.73</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="C1218" t="n">
-        <v>12.77</v>
+        <v>12.77000045776367</v>
       </c>
       <c r="D1218" t="n">
-        <v>12.28</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="E1218" t="n">
-        <v>12.37</v>
+        <v>12.36999988555908</v>
       </c>
       <c r="F1218" t="n">
         <v>17814604</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>36567131</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1219"/>
+  <dimension ref="A1:F1220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24792,19 +24792,39 @@
         <v>46321</v>
       </c>
       <c r="B1219" t="n">
-        <v>11.35</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="C1219" t="n">
-        <v>11.51</v>
+        <v>11.51000022888184</v>
       </c>
       <c r="D1219" t="n">
-        <v>10.05</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="E1219" t="n">
-        <v>10.05</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="F1219" t="n">
         <v>36567131</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>19193754</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1220"/>
+  <dimension ref="A1:F1221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24815,16 +24815,36 @@
         <v>11</v>
       </c>
       <c r="C1220" t="n">
-        <v>11.54</v>
+        <v>11.53999996185303</v>
       </c>
       <c r="D1220" t="n">
-        <v>10.99</v>
+        <v>11</v>
       </c>
       <c r="E1220" t="n">
-        <v>11.52</v>
+        <v>11.52000045776367</v>
       </c>
       <c r="F1220" t="n">
         <v>19193754</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>18318589</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1221"/>
+  <dimension ref="A1:F1222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24832,19 +24832,39 @@
         <v>46323</v>
       </c>
       <c r="B1221" t="n">
-        <v>10.7</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="C1221" t="n">
-        <v>11.03</v>
+        <v>11.02999973297119</v>
       </c>
       <c r="D1221" t="n">
-        <v>10.63</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="E1221" t="n">
-        <v>11.02</v>
+        <v>11.02000045776367</v>
       </c>
       <c r="F1221" t="n">
         <v>18318589</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>8713181</v>
       </c>
     </row>
   </sheetData>

--- a/database/ROXO34.xlsx
+++ b/database/ROXO34.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1222"/>
+  <dimension ref="A1:F1223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24852,19 +24852,39 @@
         <v>46324</v>
       </c>
       <c r="B1222" t="n">
-        <v>10.8</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="C1222" t="n">
-        <v>10.88</v>
+        <v>10.88000011444092</v>
       </c>
       <c r="D1222" t="n">
-        <v>10.55</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="E1222" t="n">
-        <v>10.55</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="F1222" t="n">
         <v>8713181</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1223" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>14885141</v>
       </c>
     </row>
   </sheetData>
